--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/TENNESSEE_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/TENNESSEE_2013.xlsx
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C121">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C270">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C654">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C747">
@@ -14442,7 +14442,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C783">
@@ -21912,7 +21912,7 @@
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1198">
